--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>77.8644</v>
+        <v>67.746</v>
       </c>
       <c r="E2" t="n">
-        <v>64.3108</v>
+        <v>45.9521</v>
       </c>
       <c r="F2" t="n">
-        <v>13.5534</v>
+        <v>21.7939</v>
       </c>
       <c r="G2" t="n">
-        <v>34.585</v>
+        <v>43.1968</v>
       </c>
       <c r="H2" t="n">
-        <v>31.1988</v>
+        <v>27.1852</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3865</v>
+        <v>16.0114</v>
       </c>
       <c r="J2" t="n">
-        <v>58.7045</v>
+        <v>66.48909999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>48.1464</v>
+        <v>47.263</v>
       </c>
       <c r="L2" t="n">
-        <v>10.558</v>
+        <v>19.2259</v>
       </c>
       <c r="M2" t="n">
-        <v>-24.1197</v>
+        <v>-23.2923</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.9477</v>
+        <v>-20.0778</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.172000000000001</v>
+        <v>-3.2148</v>
       </c>
       <c r="P2" t="n">
-        <v>-10.5755</v>
+        <v>-4.8962</v>
       </c>
       <c r="Q2" t="n">
-        <v>-56.9919</v>
+        <v>-60.5171</v>
       </c>
       <c r="R2" t="n">
-        <v>46.416</v>
+        <v>55.6206</v>
       </c>
       <c r="S2" t="n">
-        <v>69.5029</v>
+        <v>4.307</v>
       </c>
       <c r="T2" t="n">
-        <v>57.7301</v>
+        <v>3.3475</v>
       </c>
       <c r="U2" t="n">
-        <v>11.7732</v>
+        <v>0.9596</v>
       </c>
       <c r="V2" t="n">
-        <v>-15.6479</v>
+        <v>25.1388</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8685</v>
+        <v>36.6332</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.5164</v>
+        <v>-11.4945</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>55.9306</v>
+        <v>66.6919</v>
       </c>
       <c r="E3" t="n">
-        <v>51.4461</v>
+        <v>58.5467</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4844</v>
+        <v>8.145</v>
       </c>
       <c r="G3" t="n">
         <v>43.1286</v>
@@ -688,13 +688,13 @@
         <v>25.852</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.1502</v>
+        <v>-0.3892000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.8401</v>
+        <v>0.2605999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.3102</v>
+        <v>-0.6496</v>
       </c>
       <c r="V3" t="n">
         <v>16.3143</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>52.2173</v>
+        <v>43.1468</v>
       </c>
       <c r="E4" t="n">
-        <v>34.7885</v>
+        <v>41.1933</v>
       </c>
       <c r="F4" t="n">
-        <v>17.4287</v>
+        <v>1.9533</v>
       </c>
       <c r="G4" t="n">
-        <v>43.1968</v>
+        <v>10.0358</v>
       </c>
       <c r="H4" t="n">
-        <v>27.1852</v>
+        <v>9.434799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>16.0114</v>
+        <v>0.6010000000000006</v>
       </c>
       <c r="J4" t="n">
-        <v>66.48909999999999</v>
+        <v>50.5228</v>
       </c>
       <c r="K4" t="n">
-        <v>47.263</v>
+        <v>33.9784</v>
       </c>
       <c r="L4" t="n">
-        <v>19.2259</v>
+        <v>16.5442</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.2923</v>
+        <v>-40.4868</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.0778</v>
+        <v>-24.5437</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2148</v>
+        <v>-15.9437</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.8962</v>
+        <v>14.4925</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60.5171</v>
+        <v>-42.6946</v>
       </c>
       <c r="R4" t="n">
-        <v>55.6206</v>
+        <v>57.1874</v>
       </c>
       <c r="S4" t="n">
-        <v>-11.2221</v>
+        <v>-0.4628</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.8164</v>
+        <v>1.2085</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.4059</v>
+        <v>-1.6714</v>
       </c>
       <c r="V4" t="n">
-        <v>25.1388</v>
+        <v>19.0808</v>
       </c>
       <c r="W4" t="n">
-        <v>36.6332</v>
+        <v>32.1575</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.4945</v>
+        <v>-13.0768</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>40.647</v>
+        <v>38.8492</v>
       </c>
       <c r="E5" t="n">
-        <v>33.3153</v>
+        <v>30.4165</v>
       </c>
       <c r="F5" t="n">
-        <v>7.331300000000001</v>
+        <v>8.433</v>
       </c>
       <c r="G5" t="n">
         <v>-15.5795</v>
@@ -844,13 +844,13 @@
         <v>52.2913</v>
       </c>
       <c r="S5" t="n">
-        <v>18.727</v>
+        <v>16.9293</v>
       </c>
       <c r="T5" t="n">
-        <v>14.4513</v>
+        <v>11.5524</v>
       </c>
       <c r="U5" t="n">
-        <v>4.2754</v>
+        <v>5.3767</v>
       </c>
       <c r="V5" t="n">
         <v>18.1105</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. PETERS</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>19.1925</v>
+        <v>38.4444</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5269</v>
+        <v>29.1598</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6655</v>
+        <v>9.2845</v>
       </c>
       <c r="G6" t="n">
-        <v>7.878300000000001</v>
+        <v>34.585</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3296</v>
+        <v>31.1988</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5488</v>
+        <v>3.3865</v>
       </c>
       <c r="J6" t="n">
-        <v>10.5911</v>
+        <v>58.7045</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2619</v>
+        <v>48.1464</v>
       </c>
       <c r="L6" t="n">
-        <v>4.3291</v>
+        <v>10.558</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7127</v>
+        <v>-24.1197</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9323999999999999</v>
+        <v>-16.9477</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7804</v>
+        <v>-7.172000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3917</v>
+        <v>-10.5755</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.008900000000001</v>
+        <v>-56.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>8.6173</v>
+        <v>46.416</v>
       </c>
       <c r="S6" t="n">
-        <v>12.4165</v>
+        <v>30.0832</v>
       </c>
       <c r="T6" t="n">
-        <v>8.685700000000001</v>
+        <v>22.5789</v>
       </c>
       <c r="U6" t="n">
-        <v>3.731</v>
+        <v>7.5042</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7108999999999999</v>
+        <v>-15.6479</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2594</v>
+        <v>4.8685</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.9703</v>
+        <v>-20.5164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>R. PETERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>10.0212</v>
+        <v>11.2756</v>
       </c>
       <c r="E7" t="n">
-        <v>16.0094</v>
+        <v>7.855399999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.988</v>
+        <v>3.420100000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>10.0358</v>
+        <v>7.878300000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>9.434799999999999</v>
+        <v>5.3296</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6010000000000006</v>
+        <v>2.5488</v>
       </c>
       <c r="J7" t="n">
-        <v>50.5228</v>
+        <v>10.5911</v>
       </c>
       <c r="K7" t="n">
-        <v>33.9784</v>
+        <v>6.2619</v>
       </c>
       <c r="L7" t="n">
-        <v>16.5442</v>
+        <v>4.3291</v>
       </c>
       <c r="M7" t="n">
-        <v>-40.4868</v>
+        <v>-2.7127</v>
       </c>
       <c r="N7" t="n">
-        <v>-24.5437</v>
+        <v>-0.9323999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-15.9437</v>
+        <v>-1.7804</v>
       </c>
       <c r="P7" t="n">
-        <v>14.4925</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-42.6946</v>
+        <v>-9.008900000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>57.1874</v>
+        <v>8.6173</v>
       </c>
       <c r="S7" t="n">
-        <v>-33.5882</v>
+        <v>4.4999</v>
       </c>
       <c r="T7" t="n">
-        <v>-23.9756</v>
+        <v>3.0142</v>
       </c>
       <c r="U7" t="n">
-        <v>-9.6127</v>
+        <v>1.4857</v>
       </c>
       <c r="V7" t="n">
-        <v>19.0808</v>
+        <v>-0.7108999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>32.1575</v>
+        <v>3.2594</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.0768</v>
+        <v>-3.9703</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. OKEKE</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>8.514200000000001</v>
+        <v>8.081299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>7.3312</v>
+        <v>5.2944</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1829</v>
+        <v>2.7866</v>
       </c>
       <c r="G8" t="n">
-        <v>7.291</v>
+        <v>7.837699999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>5.753</v>
+        <v>2.5864</v>
       </c>
       <c r="I8" t="n">
-        <v>1.538</v>
+        <v>5.2513</v>
       </c>
       <c r="J8" t="n">
-        <v>11.8109</v>
+        <v>14.4703</v>
       </c>
       <c r="K8" t="n">
-        <v>10.964</v>
+        <v>8.119100000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8469999999999998</v>
+        <v>6.3511</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.52</v>
+        <v>-6.6327</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.2111</v>
+        <v>-5.5329</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6910999999999998</v>
+        <v>-1.0997</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.0506</v>
+        <v>-3.525300000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-18.0181</v>
+        <v>-20.7599</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9675</v>
+        <v>17.2345</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7831</v>
+        <v>-0.3879999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7619</v>
+        <v>1.1405</v>
       </c>
       <c r="U8" t="n">
-        <v>3.0212</v>
+        <v>-1.5286</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4907</v>
+        <v>4.157</v>
       </c>
       <c r="W8" t="n">
-        <v>10.7768</v>
+        <v>10.4439</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.2859</v>
+        <v>-6.2869</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HERNANDEZ GARCIA</t>
+          <t>I. OKEKE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6.5776</v>
+        <v>5.414999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3628</v>
+        <v>5.6079</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2148</v>
+        <v>-0.1930999999999998</v>
       </c>
       <c r="G9" t="n">
-        <v>4.592</v>
+        <v>7.291</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1626</v>
+        <v>5.753</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4294</v>
+        <v>1.538</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4869</v>
+        <v>11.8109</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1595</v>
+        <v>10.964</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6726</v>
+        <v>0.8469999999999998</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1051</v>
+        <v>-4.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0031</v>
+        <v>-5.2111</v>
       </c>
       <c r="O9" t="n">
-        <v>1.102</v>
+        <v>0.6910999999999998</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7419</v>
+        <v>-7.0506</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.917</v>
+        <v>-18.0181</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1751</v>
+        <v>10.9675</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3524</v>
+        <v>2.6837</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6327</v>
+        <v>1.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7196</v>
+        <v>1.6451</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6248</v>
+        <v>2.4907</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1602</v>
+        <v>10.7768</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.785</v>
+        <v>-8.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NGUFOR</t>
+          <t>S. HERNANDEZ GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.994600000000001</v>
+        <v>4.2312</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3145</v>
+        <v>2.2302</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.32</v>
+        <v>2.0009</v>
       </c>
       <c r="G10" t="n">
-        <v>1.431</v>
+        <v>4.592</v>
       </c>
       <c r="H10" t="n">
-        <v>8.916399999999999</v>
+        <v>4.1626</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.4854</v>
+        <v>0.4294</v>
       </c>
       <c r="J10" t="n">
-        <v>14.8932</v>
+        <v>3.4869</v>
       </c>
       <c r="K10" t="n">
-        <v>14.1368</v>
+        <v>4.1595</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7564999999999997</v>
+        <v>-0.6726</v>
       </c>
       <c r="M10" t="n">
-        <v>-13.4622</v>
+        <v>1.1051</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.220499999999999</v>
+        <v>0.0031</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.2417</v>
+        <v>1.102</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.400700000000001</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.8429</v>
+        <v>-3.917</v>
       </c>
       <c r="R10" t="n">
-        <v>7.4422</v>
+        <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>8.547699999999999</v>
+        <v>3.006</v>
       </c>
       <c r="T10" t="n">
-        <v>5.760800000000001</v>
+        <v>2.5002</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7871</v>
+        <v>0.5058</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4166</v>
+        <v>-0.6248</v>
       </c>
       <c r="W10" t="n">
-        <v>8.5037</v>
+        <v>0.1602</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.0871</v>
+        <v>-0.785</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6236999999999999</v>
+        <v>0.8625</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6006</v>
+        <v>-1.4983</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2244</v>
+        <v>2.3608</v>
       </c>
       <c r="G11" t="n">
         <v>0.1295</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.7162999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6580999999999999</v>
+        <v>-0.5216</v>
       </c>
       <c r="V11" t="n">
         <v>0.6659</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5036</v>
+        <v>0.6432</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0186</v>
+        <v>0.0408</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5222</v>
+        <v>0.6024</v>
       </c>
       <c r="G12" t="n">
         <v>0.3137</v>
@@ -1390,13 +1390,13 @@
         <v>0.1958</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0059</v>
+        <v>0.1337</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0594</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>J. NGUFOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7419000000000002</v>
+        <v>-0.4331999999999994</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9613</v>
+        <v>10.215</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2197</v>
+        <v>-10.6481</v>
       </c>
       <c r="G13" t="n">
-        <v>7.837699999999999</v>
+        <v>1.431</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5864</v>
+        <v>8.916399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2513</v>
+        <v>-7.4854</v>
       </c>
       <c r="J13" t="n">
-        <v>14.4703</v>
+        <v>14.8932</v>
       </c>
       <c r="K13" t="n">
-        <v>8.119100000000001</v>
+        <v>14.1368</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3511</v>
+        <v>0.7564999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6327</v>
+        <v>-13.4622</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.5329</v>
+        <v>-5.220499999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0997</v>
+        <v>-8.2417</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.525300000000001</v>
+        <v>-9.400700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.7599</v>
+        <v>-16.8429</v>
       </c>
       <c r="R13" t="n">
-        <v>17.2345</v>
+        <v>7.4422</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.2111</v>
+        <v>5.12</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.1154</v>
+        <v>3.6611</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0956</v>
+        <v>1.4587</v>
       </c>
       <c r="V13" t="n">
-        <v>4.157</v>
+        <v>2.4166</v>
       </c>
       <c r="W13" t="n">
-        <v>10.4439</v>
+        <v>8.5037</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.2869</v>
+        <v>-6.0871</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>D. PALACIOS AQUINO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2462</v>
+        <v>-2.3053</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6993000000000009</v>
+        <v>-2.3427</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9452</v>
+        <v>0.03739999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.8384</v>
+        <v>-1.0471</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.3855</v>
+        <v>-0.2236</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4529000000000001</v>
+        <v>-0.8236</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5605</v>
+        <v>-0.1731</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3388000000000003</v>
+        <v>0.3879</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8994</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.399</v>
+        <v>-0.8740000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0468</v>
+        <v>-0.6115</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3524</v>
+        <v>-0.2626</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7833</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.8338</v>
+        <v>-1.9584</v>
       </c>
       <c r="R14" t="n">
-        <v>8.617100000000001</v>
+        <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2295</v>
+        <v>0.1127</v>
       </c>
       <c r="T14" t="n">
-        <v>5.756</v>
+        <v>-0.2111</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5265</v>
+        <v>0.324</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4208</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.6374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9017</v>
+        <v>-2.3599</v>
       </c>
       <c r="E15" t="n">
-        <v>0.277</v>
+        <v>-0.2347</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1786</v>
+        <v>-2.1252</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8924</v>
@@ -1624,13 +1624,13 @@
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.3367</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0081</v>
+        <v>0.4964</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2166</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PALACIOS AQUINO</t>
+          <t>J. BUENO DE LA ROSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4297</v>
+        <v>-3.284</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5474</v>
+        <v>-1.4034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1177</v>
+        <v>-1.881</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0471</v>
+        <v>-3.9921</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2236</v>
+        <v>-1.1832</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8236</v>
+        <v>-2.809</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1731</v>
+        <v>-1.1099</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3879</v>
+        <v>-0.4374</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.6726000000000002</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8740000000000001</v>
+        <v>-2.8824</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6115</v>
+        <v>-0.7458</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2626</v>
+        <v>-2.1366</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3709</v>
+        <v>1.7624</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9584</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5875</v>
+        <v>1.7624</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0117</v>
+        <v>-0.171</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4158</v>
+        <v>-0.2935</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4041</v>
+        <v>0.1226</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BUENO DE LA ROSA</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1991</v>
+        <v>-3.8481</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1791</v>
+        <v>-2.5263</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.02</v>
+        <v>-1.3222</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.9921</v>
+        <v>-3.8384</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1832</v>
+        <v>-3.3855</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.809</v>
+        <v>-0.4529000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1099</v>
+        <v>1.5605</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4374</v>
+        <v>-0.3388000000000003</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6726000000000002</v>
+        <v>1.8994</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8824</v>
+        <v>-5.399</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7458</v>
+        <v>-3.0468</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1366</v>
+        <v>-2.3524</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7624</v>
+        <v>0.7833</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-7.8338</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7624</v>
+        <v>8.617100000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0859</v>
+        <v>1.6275</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0692</v>
+        <v>2.5308</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.01669999999999992</v>
+        <v>-0.9032999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8837</v>
+        <v>-2.4208</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8837</v>
+        <v>-3.6374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MELGAR ZORITA</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.6346</v>
+        <v>-4.6717</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1317</v>
+        <v>8.6694</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.503</v>
+        <v>-13.341</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2343</v>
+        <v>3.805800000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0878</v>
+        <v>8.8154</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1465</v>
+        <v>-5.0095</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0446</v>
+        <v>20.3326</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8221</v>
+        <v>19.7919</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7775000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1897</v>
+        <v>-16.5267</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2656</v>
+        <v>-10.9763</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9240999999999999</v>
+        <v>-5.5505</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7834</v>
+        <v>-0.7833999999999994</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9584</v>
+        <v>-18.018</v>
       </c>
       <c r="R18" t="n">
-        <v>1.175</v>
+        <v>17.2343</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1839</v>
+        <v>3.0232</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1286</v>
+        <v>4.266900000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0553</v>
+        <v>-1.2435</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4332</v>
+        <v>-10.7175</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.0878</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4332</v>
+        <v>-12.8053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>M. MELGAR ZORITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.0642</v>
+        <v>-6.5589</v>
       </c>
       <c r="E19" t="n">
-        <v>8.910300000000001</v>
+        <v>-3.62</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.9748</v>
+        <v>-2.9388</v>
       </c>
       <c r="G19" t="n">
-        <v>3.805800000000001</v>
+        <v>-2.2343</v>
       </c>
       <c r="H19" t="n">
-        <v>8.8154</v>
+        <v>-2.0878</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.0095</v>
+        <v>-0.1465</v>
       </c>
       <c r="J19" t="n">
-        <v>20.3326</v>
+        <v>-1.0446</v>
       </c>
       <c r="K19" t="n">
-        <v>19.7919</v>
+        <v>-1.8221</v>
       </c>
       <c r="L19" t="n">
-        <v>0.541</v>
+        <v>0.7775000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-16.5267</v>
+        <v>-1.1897</v>
       </c>
       <c r="N19" t="n">
-        <v>-10.9763</v>
+        <v>-0.2656</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.5505</v>
+        <v>-0.9240999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7833999999999994</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-18.018</v>
+        <v>-1.9584</v>
       </c>
       <c r="R19" t="n">
-        <v>17.2343</v>
+        <v>1.175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3692999999999998</v>
+        <v>-1.108</v>
       </c>
       <c r="T19" t="n">
-        <v>4.508100000000001</v>
+        <v>-0.6169</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.8773</v>
+        <v>-0.4911</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.7175</v>
+        <v>-2.4332</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0878</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.8053</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.881400000000001</v>
+        <v>-6.783300000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.2411</v>
+        <v>-8.121600000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3597</v>
+        <v>1.3385</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7529000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>9.204699999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3451</v>
+        <v>1.7531</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.349</v>
+        <v>0.7705</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0038</v>
+        <v>0.9827</v>
       </c>
       <c r="V20" t="n">
         <v>-4.2582</v>
@@ -2047,13 +2047,13 @@
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.5584</v>
+        <v>-12.2817</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.188000000000001</v>
+        <v>-4.860499999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.3705</v>
+        <v>-7.4209</v>
       </c>
       <c r="G21" t="n">
         <v>-1.628</v>
@@ -2092,13 +2092,13 @@
         <v>12.9258</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.6986</v>
+        <v>-1.4218</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.8018</v>
+        <v>-0.4745000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8966</v>
+        <v>-0.9471999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-10.9945</v>
@@ -2125,13 +2125,13 @@
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>-15.589</v>
+        <v>-12.8125</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7692</v>
+        <v>-1.9637</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.8196</v>
+        <v>-10.8487</v>
       </c>
       <c r="G22" t="n">
         <v>-11.3269</v>
@@ -2170,13 +2170,13 @@
         <v>11.3591</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1474000000000002</v>
+        <v>2.6289</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1806000000000001</v>
+        <v>1.9861</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3278</v>
+        <v>0.6427999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>2.3488</v>
@@ -2203,13 +2203,13 @@
         <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.1346</v>
+        <v>-15.8447</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.516</v>
+        <v>-5.0762</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.6186</v>
+        <v>-10.7684</v>
       </c>
       <c r="G23" t="n">
         <v>-3.447900000000001</v>
@@ -2248,13 +2248,13 @@
         <v>14.2968</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.1778</v>
+        <v>1.1123</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.6512</v>
+        <v>1.7884</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.5263</v>
+        <v>-0.6763000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-11.9422</v>
@@ -2281,13 +2281,13 @@
         <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>184.7059</v>
+        <v>214.2038</v>
       </c>
       <c r="E24" t="n">
-        <v>203.1391</v>
+        <v>213.5341</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.4336</v>
+        <v>0.669000000000004</v>
       </c>
       <c r="G24" t="n">
         <v>119.4857</v>
@@ -2317,7 +2317,7 @@
         <v>-70.70160000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.855399999999999</v>
+        <v>-6.855400000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-368.1935</v>
@@ -2326,13 +2326,13 @@
         <v>361.3375</v>
       </c>
       <c r="S24" t="n">
-        <v>43.2017</v>
+        <v>72.70010000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>49.9558</v>
+        <v>60.3509</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.753200000000001</v>
+        <v>12.3493</v>
       </c>
       <c r="V24" t="n">
         <v>28.87309999999999</v>
